--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_Auto_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_Auto_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.43766403570547</v>
+        <v>2.437745244794388</v>
       </c>
       <c r="C2">
-        <v>1.700078601593717</v>
+        <v>1.693446711233219</v>
       </c>
       <c r="D2">
-        <v>1.456920224378267</v>
+        <v>1.453366582370714</v>
       </c>
       <c r="E2">
-        <v>1.346585525682575</v>
+        <v>1.346145053135311</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.444871584426221</v>
+        <v>2.444889620773036</v>
       </c>
       <c r="C3">
-        <v>1.703624045046674</v>
+        <v>1.696783916929245</v>
       </c>
       <c r="D3">
-        <v>1.458610037681003</v>
+        <v>1.455025691607578</v>
       </c>
       <c r="E3">
-        <v>1.347817107110186</v>
+        <v>1.347368296397462</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.41651902216063</v>
+        <v>2.416507841655045</v>
       </c>
       <c r="C4">
-        <v>1.689118343792704</v>
+        <v>1.682414734277926</v>
       </c>
       <c r="D4">
-        <v>1.451047547992394</v>
+        <v>1.447527665020967</v>
       </c>
       <c r="E4">
-        <v>1.342443321396813</v>
+        <v>1.341988648295406</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.446396964240129</v>
+        <v>2.44639883729947</v>
       </c>
       <c r="C5">
-        <v>1.705623931229837</v>
+        <v>1.698637703165205</v>
       </c>
       <c r="D5">
-        <v>1.446216490933228</v>
+        <v>1.442563428392502</v>
       </c>
       <c r="E5">
-        <v>1.350032931609149</v>
+        <v>1.349527612582106</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2.453820867654346</v>
+        <v>2.453822867390262</v>
       </c>
       <c r="C6">
-        <v>1.709811521561945</v>
+        <v>1.702778181237995</v>
       </c>
       <c r="D6">
-        <v>1.448875947771871</v>
+        <v>1.445187114311787</v>
       </c>
       <c r="E6">
-        <v>1.352104465373867</v>
+        <v>1.351597290893297</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.445607710036876</v>
+        <v>2.445611685535605</v>
       </c>
       <c r="C7">
-        <v>1.705657750267797</v>
+        <v>1.698693551260726</v>
       </c>
       <c r="D7">
-        <v>1.461064592524589</v>
+        <v>1.457382261472365</v>
       </c>
       <c r="E7">
-        <v>1.3502050541849</v>
+        <v>1.349728347175503</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.428272206215447</v>
+        <v>2.428379668241469</v>
       </c>
       <c r="C8">
-        <v>1.691569675101092</v>
+        <v>1.685498628784307</v>
       </c>
       <c r="D8">
-        <v>1.463279494679763</v>
+        <v>1.460950178653511</v>
       </c>
       <c r="E8">
-        <v>1.34067164994444</v>
+        <v>1.34053287489543</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.438785451754285</v>
+        <v>2.438794020602139</v>
       </c>
       <c r="C9">
-        <v>1.699117520271849</v>
+        <v>1.692202314332432</v>
       </c>
       <c r="D9">
-        <v>1.455019439359379</v>
+        <v>1.451387656235327</v>
       </c>
       <c r="E9">
-        <v>1.344961376309288</v>
+        <v>1.344502126473592</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.350206967072475</v>
+        <v>2.350190879935348</v>
       </c>
       <c r="C10">
-        <v>1.664463245616165</v>
+        <v>1.658377414931971</v>
       </c>
       <c r="D10">
-        <v>1.44357601379494</v>
+        <v>1.440095572654453</v>
       </c>
       <c r="E10">
-        <v>1.33803734195631</v>
+        <v>1.337604876518737</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2.355463786409342</v>
+        <v>2.357987329780411</v>
       </c>
       <c r="C11">
-        <v>1.670736457539432</v>
+        <v>1.664602016793604</v>
       </c>
       <c r="D11">
-        <v>1.44699511323945</v>
+        <v>1.443486738685015</v>
       </c>
       <c r="E11">
-        <v>1.339872308311111</v>
+        <v>1.339440020619098</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2.232917583795265</v>
+        <v>2.233045188575209</v>
       </c>
       <c r="C12">
-        <v>1.617529040115271</v>
+        <v>1.611899663964373</v>
       </c>
       <c r="D12">
-        <v>1.42465114317971</v>
+        <v>1.421227856922761</v>
       </c>
       <c r="E12">
-        <v>1.324747553747766</v>
+        <v>1.324309626005364</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.338634367234773</v>
+        <v>2.338618296386124</v>
       </c>
       <c r="C13">
-        <v>1.65828505256153</v>
+        <v>1.651970098391188</v>
       </c>
       <c r="D13">
-        <v>1.440235713151947</v>
+        <v>1.436759568958574</v>
       </c>
       <c r="E13">
-        <v>1.335620606451475</v>
+        <v>1.335180309218462</v>
       </c>
     </row>
   </sheetData>
